--- a/astro-site/public/dl/pack-appcc/16-registro-coccion-regeneracion.xlsx
+++ b/astro-site/public/dl/pack-appcc/16-registro-coccion-regeneracion.xlsx
@@ -1486,13 +1486,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A49:J49"/>
     <mergeCell ref="A51:J51"/>
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A50:J50"/>
     <mergeCell ref="A46:J46"/>
-    <mergeCell ref="A50:J50"/>
     <mergeCell ref="A47:J47"/>
     <mergeCell ref="A48:J48"/>
-    <mergeCell ref="A49:J49"/>
+    <mergeCell ref="A1:J1"/>
   </mergeCells>
   <conditionalFormatting sqref="H5:H44">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
